--- a/cet4/result/31_重生商女_千亿女王的商业帝国/31_重生商女_千亿女王的商业帝国_学习版.xlsx
+++ b/cet4/result/31_重生商女_千亿女王的商业帝国/31_重生商女_千亿女王的商业帝国_学习版.xlsx
@@ -397,1109 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>china</v>
       </c>
       <c r="B2" t="str">
-        <v>china</v>
+        <v>/ˈtʃaɪnə/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>瓷器</v>
       </c>
-      <c r="D2" t="str">
-        <v>china(瓷器)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>recent</v>
       </c>
       <c r="B3" t="str">
-        <v>recent</v>
+        <v>/ˈriːsnt/</v>
       </c>
       <c r="C3" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>最近的</v>
       </c>
-      <c r="D3" t="str">
-        <v>recent(最近的)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>beginner</v>
       </c>
       <c r="B4" t="str">
-        <v>beginner</v>
+        <v>/bɪˈɡɪnər/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>新手</v>
       </c>
-      <c r="D4" t="str">
-        <v>beginner(新手)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>amongst</v>
       </c>
       <c r="B5" t="str">
-        <v>amongst</v>
+        <v>/əˈmʌŋst/</v>
       </c>
       <c r="C5" t="str">
+        <v>prep.</v>
+      </c>
+      <c r="D5" t="str">
         <v>在……当中</v>
       </c>
-      <c r="D5" t="str">
-        <v>amongst(在……当中)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>heart</v>
       </c>
       <c r="B6" t="str">
-        <v>heart</v>
+        <v>/hɑːrt/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>心脏</v>
       </c>
-      <c r="D6" t="str">
-        <v>heart(心脏)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>odour</v>
       </c>
       <c r="B7" t="str">
-        <v>odour</v>
+        <v>/ˈoʊdər/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>气味</v>
       </c>
-      <c r="D7" t="str">
-        <v>odour(气味)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>kettle</v>
       </c>
       <c r="B8" t="str">
-        <v>kettle</v>
+        <v>/ˈketl/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>壶</v>
       </c>
-      <c r="D8" t="str">
-        <v>kettle(壶)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>listen</v>
       </c>
       <c r="B9" t="str">
-        <v>listen</v>
+        <v>/ˈlɪsn/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>倾听</v>
       </c>
-      <c r="D9" t="str">
-        <v>listen(倾听)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>contract</v>
       </c>
       <c r="B10" t="str">
-        <v>contract</v>
+        <v>/ˈkɑːntrækt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D10" t="str">
         <v>合同</v>
       </c>
-      <c r="D10" t="str">
-        <v>contract(合同)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>recently</v>
       </c>
       <c r="B11" t="str">
-        <v>recently</v>
+        <v>/ˈriːsntli/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D11" t="str">
         <v>最近</v>
       </c>
-      <c r="D11" t="str">
-        <v>recently(最近)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>undertake</v>
       </c>
       <c r="B12" t="str">
-        <v>beginner</v>
+        <v>/ˌʌndərˈteɪk/</v>
       </c>
       <c r="C12" t="str">
-        <v>新手</v>
+        <v>vt.</v>
       </c>
       <c r="D12" t="str">
-        <v>beginner(新手)📢</v>
+        <v>承担</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>mineral</v>
       </c>
       <c r="B13" t="str">
-        <v>undertake</v>
+        <v>/ˈmɪnərəl/</v>
       </c>
       <c r="C13" t="str">
-        <v>承担</v>
+        <v>n./adj.</v>
       </c>
       <c r="D13" t="str">
-        <v>undertake(承担)📢</v>
+        <v>矿物</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>copper</v>
       </c>
       <c r="B14" t="str">
-        <v>mineral</v>
+        <v>/ˈkɑːpər/</v>
       </c>
       <c r="C14" t="str">
-        <v>矿物</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D14" t="str">
-        <v>mineral(矿物)📢</v>
+        <v>铜</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>conversely</v>
       </c>
       <c r="B15" t="str">
-        <v>copper</v>
+        <v>/ˈkɑːnvɜːrsli/</v>
       </c>
       <c r="C15" t="str">
-        <v>铜</v>
+        <v>v./adv.</v>
       </c>
       <c r="D15" t="str">
-        <v>copper(铜)📢</v>
+        <v>相反地</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>might</v>
       </c>
       <c r="B16" t="str">
-        <v>contract</v>
+        <v>/maɪt/</v>
       </c>
       <c r="C16" t="str">
-        <v>合同</v>
+        <v>n./aux.</v>
       </c>
       <c r="D16" t="str">
-        <v>contract(合同)📢</v>
+        <v>可能</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>accordingly</v>
       </c>
       <c r="B17" t="str">
-        <v>conversely</v>
+        <v>/əˈkɔːrdɪŋli/</v>
       </c>
       <c r="C17" t="str">
-        <v>相反地</v>
+        <v>v./adv.</v>
       </c>
       <c r="D17" t="str">
-        <v>conversely(相反地)📢</v>
+        <v>因此</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>action</v>
       </c>
       <c r="B18" t="str">
-        <v>might</v>
+        <v>/ˈækʃn/</v>
       </c>
       <c r="C18" t="str">
-        <v>可能</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>might(可能)📢</v>
+        <v>行动</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>blackboard</v>
       </c>
       <c r="B19" t="str">
-        <v>accordingly</v>
+        <v>/ˈblækbɔːrd/</v>
       </c>
       <c r="C19" t="str">
-        <v>因此</v>
+        <v>n.</v>
       </c>
       <c r="D19" t="str">
-        <v>accordingly(因此)📢</v>
+        <v>黑板</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>pressure</v>
       </c>
       <c r="B20" t="str">
-        <v>action</v>
+        <v>/ˈpreʃər/</v>
       </c>
       <c r="C20" t="str">
-        <v>行动</v>
+        <v>n./vt.</v>
       </c>
       <c r="D20" t="str">
-        <v>action(行动)📢</v>
+        <v>压力</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>compound</v>
       </c>
       <c r="B21" t="str">
-        <v>blackboard</v>
+        <v>/ˈkɑːmpaʊnd/</v>
       </c>
       <c r="C21" t="str">
-        <v>黑板</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D21" t="str">
-        <v>blackboard(黑板)📢</v>
+        <v>化合物</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>Fahrenheit</v>
       </c>
       <c r="B22" t="str">
-        <v>pressure</v>
+        <v>/ˈfærənhaɪt/</v>
       </c>
       <c r="C22" t="str">
-        <v>压力</v>
+        <v>n./adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>pressure(压力)📢</v>
+        <v>华氏温度</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>gas</v>
       </c>
       <c r="B23" t="str">
-        <v>undertake</v>
+        <v>/ɡæs/</v>
       </c>
       <c r="C23" t="str">
-        <v>承担</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D23" t="str">
-        <v>undertake(承担)📢</v>
+        <v>气体</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>official</v>
       </c>
       <c r="B24" t="str">
-        <v>beginner</v>
+        <v>/əˈfɪʃl/</v>
       </c>
       <c r="C24" t="str">
-        <v>新手</v>
+        <v>n./adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>beginner(新手)📢</v>
+        <v>官员</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>balloon</v>
       </c>
       <c r="B25" t="str">
-        <v>compound</v>
+        <v>/bəˈluːn/</v>
       </c>
       <c r="C25" t="str">
-        <v>化合物</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>compound(化合物)📢</v>
+        <v>气球</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>around</v>
       </c>
       <c r="B26" t="str">
-        <v>compound</v>
+        <v>/əˈraʊnd/</v>
       </c>
       <c r="C26" t="str">
-        <v>化合物</v>
+        <v>v./adv./prep.</v>
       </c>
       <c r="D26" t="str">
-        <v>compound(化合物)📢</v>
+        <v>周围</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>something</v>
       </c>
       <c r="B27" t="str">
-        <v>Fahrenheit</v>
+        <v>/ˈsʌmθɪŋ/</v>
       </c>
       <c r="C27" t="str">
-        <v>华氏温度</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D27" t="str">
-        <v>Fahrenheit(华氏温度)📢</v>
+        <v>某事</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>toss</v>
       </c>
       <c r="B28" t="str">
-        <v>gas</v>
+        <v>/tɔːs/</v>
       </c>
       <c r="C28" t="str">
-        <v>气体</v>
+        <v>v.</v>
       </c>
       <c r="D28" t="str">
-        <v>gas(气体)📢</v>
+        <v>投</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>Greek</v>
       </c>
       <c r="B29" t="str">
-        <v>official</v>
+        <v>/ɡriːk/</v>
       </c>
       <c r="C29" t="str">
-        <v>官员</v>
+        <v>n./adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>official(官员)📢</v>
+        <v>希腊</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>either</v>
       </c>
       <c r="B30" t="str">
-        <v>china</v>
+        <v>/ˈiːðər,ˈaɪðər/</v>
       </c>
       <c r="C30" t="str">
-        <v>瓷器</v>
+        <v>n./adj./pron./conj.</v>
       </c>
       <c r="D30" t="str">
-        <v>china(瓷器)📢</v>
+        <v>任一</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>suspend</v>
       </c>
       <c r="B31" t="str">
-        <v>balloon</v>
+        <v>/səˈspend/</v>
       </c>
       <c r="C31" t="str">
-        <v>气球</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>balloon(气球)📢</v>
+        <v>暂停</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>yawn</v>
       </c>
       <c r="B32" t="str">
-        <v>odour</v>
+        <v>/jɔːn/</v>
       </c>
       <c r="C32" t="str">
-        <v>气味</v>
+        <v>n./v.</v>
       </c>
       <c r="D32" t="str">
-        <v>odour(气味)📢</v>
+        <v>打哈欠</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>exciting</v>
       </c>
       <c r="B33" t="str">
-        <v>around</v>
+        <v>/ɪkˈsaɪtɪŋ/</v>
       </c>
       <c r="C33" t="str">
-        <v>周围</v>
+        <v>v./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>around(周围)📢</v>
+        <v>令人兴奋的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>kilometer</v>
       </c>
       <c r="B34" t="str">
-        <v>official</v>
+        <v>/kɪˈlɑːmɪtər/</v>
       </c>
       <c r="C34" t="str">
-        <v>官员</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>official(官员)📢</v>
+        <v>公里</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>tongue</v>
       </c>
       <c r="B35" t="str">
-        <v>something</v>
+        <v>/tʌŋ/</v>
       </c>
       <c r="C35" t="str">
-        <v>某事</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>something(某事)📢</v>
+        <v>舌头</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>bacteria</v>
       </c>
       <c r="B36" t="str">
-        <v>toss</v>
+        <v>/bækˈtɪriə/</v>
       </c>
       <c r="C36" t="str">
-        <v>投</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>toss(投)📢</v>
+        <v>细菌</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>steep</v>
       </c>
       <c r="B37" t="str">
-        <v>Greek</v>
+        <v>/stiːp/</v>
       </c>
       <c r="C37" t="str">
-        <v>希腊</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>Greek(希腊)📢</v>
+        <v>陡峭的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>blow</v>
       </c>
       <c r="B38" t="str">
-        <v>mineral</v>
+        <v>/bloʊ/</v>
       </c>
       <c r="C38" t="str">
-        <v>矿物</v>
+        <v>n./v.</v>
       </c>
       <c r="D38" t="str">
-        <v>mineral(矿物)📢</v>
+        <v>打击</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>lest</v>
       </c>
       <c r="B39" t="str">
-        <v>either</v>
+        <v>/lest/</v>
       </c>
       <c r="C39" t="str">
-        <v>任一</v>
+        <v>conj.</v>
       </c>
       <c r="D39" t="str">
-        <v>either(任一)📢</v>
+        <v>以免</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>decade</v>
       </c>
       <c r="B40" t="str">
-        <v>might</v>
+        <v>/ˈdekeɪd,dɪˈkeɪd/</v>
       </c>
       <c r="C40" t="str">
-        <v>可能</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>might(可能)📢</v>
+        <v>十年</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>open</v>
       </c>
       <c r="B41" t="str">
-        <v>suspend</v>
+        <v>/ˈoʊpən/</v>
       </c>
       <c r="C41" t="str">
-        <v>暂停</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>suspend(暂停)📢</v>
+        <v>开放的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>influence</v>
       </c>
       <c r="B42" t="str">
-        <v>yawn</v>
+        <v>/ˈɪnfluəns/</v>
       </c>
       <c r="C42" t="str">
-        <v>打哈欠</v>
+        <v>n./vt.</v>
       </c>
       <c r="D42" t="str">
-        <v>yawn(打哈欠)📢</v>
+        <v>影响力</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>too</v>
       </c>
       <c r="B43" t="str">
-        <v>china</v>
+        <v>/tuː/</v>
       </c>
       <c r="C43" t="str">
-        <v>瓷器</v>
+        <v>v./adv.</v>
       </c>
       <c r="D43" t="str">
-        <v>china(瓷器)📢</v>
+        <v>太</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>zoo</v>
       </c>
       <c r="B44" t="str">
-        <v>exciting</v>
+        <v>/zuː/</v>
       </c>
       <c r="C44" t="str">
-        <v>令人兴奋的</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>exciting(令人兴奋的)📢</v>
+        <v>动物园</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>camel</v>
       </c>
       <c r="B45" t="str">
-        <v>mineral</v>
+        <v>/ˈkæml/</v>
       </c>
       <c r="C45" t="str">
-        <v>矿物</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D45" t="str">
-        <v>mineral(矿物)📢</v>
+        <v>骆驼</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>mode</v>
       </c>
       <c r="B46" t="str">
-        <v>kilometer</v>
+        <v>/moʊd/</v>
       </c>
       <c r="C46" t="str">
-        <v>公里</v>
+        <v>n.</v>
       </c>
       <c r="D46" t="str">
-        <v>kilometer(公里)📢</v>
+        <v>模式</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>string</v>
       </c>
       <c r="B47" t="str">
-        <v>tongue</v>
+        <v>/strɪŋ/</v>
       </c>
       <c r="C47" t="str">
-        <v>舌头</v>
+        <v>n./vt.</v>
       </c>
       <c r="D47" t="str">
-        <v>tongue(舌头)📢</v>
+        <v>线</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>distant</v>
       </c>
       <c r="B48" t="str">
-        <v>bacteria</v>
+        <v>/ˈdɪstənt/</v>
       </c>
       <c r="C48" t="str">
-        <v>细菌</v>
+        <v>adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>bacteria(细菌)📢</v>
+        <v>遥远的</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>motion</v>
       </c>
       <c r="B49" t="str">
-        <v>steep</v>
+        <v>/ˈmoʊʃn/</v>
       </c>
       <c r="C49" t="str">
-        <v>陡峭的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>steep(陡峭的)📢</v>
+        <v>动作</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>beneath</v>
       </c>
       <c r="B50" t="str">
-        <v>gas</v>
+        <v>/bɪˈniːθ/</v>
       </c>
       <c r="C50" t="str">
-        <v>气体</v>
+        <v>n./prep.</v>
       </c>
       <c r="D50" t="str">
-        <v>gas(气体)📢</v>
+        <v>在……之下</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>nature</v>
       </c>
       <c r="B51" t="str">
-        <v>blow</v>
+        <v>/ˈneɪtʃər/</v>
       </c>
       <c r="C51" t="str">
-        <v>打击</v>
+        <v>n.</v>
       </c>
       <c r="D51" t="str">
-        <v>blow(打击)📢</v>
+        <v>自然</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>shot</v>
       </c>
       <c r="B52" t="str">
-        <v>lest</v>
+        <v>/ʃɑːt/</v>
       </c>
       <c r="C52" t="str">
-        <v>以免</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D52" t="str">
-        <v>lest(以免)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>decade</v>
-      </c>
-      <c r="C53" t="str">
-        <v>十年</v>
-      </c>
-      <c r="D53" t="str">
-        <v>decade(十年)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>beginner</v>
-      </c>
-      <c r="C54" t="str">
-        <v>新手</v>
-      </c>
-      <c r="D54" t="str">
-        <v>beginner(新手)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>open</v>
-      </c>
-      <c r="C55" t="str">
-        <v>开放的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>open(开放的)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>decade</v>
-      </c>
-      <c r="C56" t="str">
-        <v>十年</v>
-      </c>
-      <c r="D56" t="str">
-        <v>decade(十年)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>heart</v>
-      </c>
-      <c r="C57" t="str">
-        <v>心脏</v>
-      </c>
-      <c r="D57" t="str">
-        <v>heart(心脏)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>conversely</v>
-      </c>
-      <c r="C58" t="str">
-        <v>相反地</v>
-      </c>
-      <c r="D58" t="str">
-        <v>conversely(相反地)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>something</v>
-      </c>
-      <c r="C59" t="str">
-        <v>某事</v>
-      </c>
-      <c r="D59" t="str">
-        <v>something(某事)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>influence</v>
-      </c>
-      <c r="C60" t="str">
-        <v>影响力</v>
-      </c>
-      <c r="D60" t="str">
-        <v>influence(影响力)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>too</v>
-      </c>
-      <c r="C61" t="str">
-        <v>太</v>
-      </c>
-      <c r="D61" t="str">
-        <v>too(太)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>zoo</v>
-      </c>
-      <c r="C62" t="str">
-        <v>动物园</v>
-      </c>
-      <c r="D62" t="str">
-        <v>zoo(动物园)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>camel</v>
-      </c>
-      <c r="C63" t="str">
-        <v>骆驼</v>
-      </c>
-      <c r="D63" t="str">
-        <v>camel(骆驼)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>camel</v>
-      </c>
-      <c r="C64" t="str">
-        <v>骆驼</v>
-      </c>
-      <c r="D64" t="str">
-        <v>camel(骆驼)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>compound</v>
-      </c>
-      <c r="C65" t="str">
-        <v>化合物</v>
-      </c>
-      <c r="D65" t="str">
-        <v>compound(化合物)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>mode</v>
-      </c>
-      <c r="C66" t="str">
-        <v>模式</v>
-      </c>
-      <c r="D66" t="str">
-        <v>mode(模式)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>string</v>
-      </c>
-      <c r="C67" t="str">
-        <v>线</v>
-      </c>
-      <c r="D67" t="str">
-        <v>string(线)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>compound</v>
-      </c>
-      <c r="C68" t="str">
-        <v>化合物</v>
-      </c>
-      <c r="D68" t="str">
-        <v>compound(化合物)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>balloon</v>
-      </c>
-      <c r="C69" t="str">
-        <v>气球</v>
-      </c>
-      <c r="D69" t="str">
-        <v>balloon(气球)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>odour</v>
-      </c>
-      <c r="C70" t="str">
-        <v>气味</v>
-      </c>
-      <c r="D70" t="str">
-        <v>odour(气味)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>distant</v>
-      </c>
-      <c r="C71" t="str">
-        <v>遥远的</v>
-      </c>
-      <c r="D71" t="str">
-        <v>distant(遥远的)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>zoo</v>
-      </c>
-      <c r="C72" t="str">
-        <v>动物园</v>
-      </c>
-      <c r="D72" t="str">
-        <v>zoo(动物园)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>camel</v>
-      </c>
-      <c r="C73" t="str">
-        <v>骆驼</v>
-      </c>
-      <c r="D73" t="str">
-        <v>camel(骆驼)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>camel</v>
-      </c>
-      <c r="C74" t="str">
-        <v>骆驼</v>
-      </c>
-      <c r="D74" t="str">
-        <v>camel(骆驼)📢</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>motion</v>
-      </c>
-      <c r="C75" t="str">
-        <v>动作</v>
-      </c>
-      <c r="D75" t="str">
-        <v>motion(动作)📢</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
-        <v>beneath</v>
-      </c>
-      <c r="C76" t="str">
-        <v>在……之下</v>
-      </c>
-      <c r="D76" t="str">
-        <v>beneath(在……之下)📢</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="str">
-        <v>nature</v>
-      </c>
-      <c r="C77" t="str">
-        <v>自然</v>
-      </c>
-      <c r="D77" t="str">
-        <v>nature(自然)📢</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="str">
-        <v>shot</v>
-      </c>
-      <c r="C78" t="str">
         <v>照片</v>
-      </c>
-      <c r="D78" t="str">
-        <v>shot(照片)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>